--- a/inst/config/artfish.xlsx
+++ b/inst/config/artfish.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/45dcb46a42df1333/Projects_COMPLETED_TEMP/2021-2024_FISH4ACP/2026_FISHERIES_STATISTICS_STP/estatisticapesqueiraSTP/inst/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/45dcb46a42df1333/Projects_COMPLETED_TEMP/2021-2024_FISH4ACP/2026_FISHERIES_STATISTICS_STP/R/estatisticapesqueiraSTP/inst/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{48924530-FE3E-40A8-BBAC-91543B265E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04107AE-080E-44D2-AD43-A3929E36DA9B}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{48924530-FE3E-40A8-BBAC-91543B265E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFF4EFD1-0774-4E12-B4D9-4D773A258C78}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{78E43024-E045-437A-8134-12618B2A0D81}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{78E43024-E045-437A-8134-12618B2A0D81}"/>
   </bookViews>
   <sheets>
     <sheet name="dat" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="46">
   <si>
     <t>embarcacoes</t>
   </si>
@@ -157,12 +157,6 @@
   </si>
   <si>
     <t>artfish_dat</t>
-  </si>
-  <si>
-    <t>distrito_origem</t>
-  </si>
-  <si>
-    <t>comunidade_origem</t>
   </si>
   <si>
     <t>embarcacoes_ativas_mensal</t>
@@ -562,13 +556,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE77F8F0-EAEA-4418-89CA-3D81770789EB}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -576,7 +570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -584,7 +578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -592,7 +586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -600,7 +594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -616,14 +610,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F26697C-152D-4326-8C29-6318F7F31226}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -637,7 +631,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -648,7 +642,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -659,7 +653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -670,7 +664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -681,7 +675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -692,7 +686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -703,7 +697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -714,7 +708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -725,7 +719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -736,7 +730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -747,7 +741,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
@@ -758,7 +752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,7 +763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
@@ -780,7 +774,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
@@ -788,10 +782,10 @@
         <v>19</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,7 +796,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -813,7 +807,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -824,7 +818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -835,7 +829,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -843,10 +837,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -854,10 +848,10 @@
         <v>21</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,7 +862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -879,7 +873,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,10 +881,10 @@
         <v>38</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>1</v>
       </c>
@@ -901,18 +895,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
@@ -923,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
@@ -934,7 +928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
@@ -945,7 +939,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
@@ -953,18 +947,18 @@
         <v>33</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
